--- a/artfynd/S 1795-2026 artfynd.xlsx
+++ b/artfynd/S 1795-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63217577</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533224</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533238</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537146</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1260,6 +1285,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537159</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1381,6 +1411,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533225</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1502,6 +1537,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533236</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1623,6 +1663,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533240</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1744,6 +1789,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533226</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1865,6 +1915,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533228</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1986,6 +2041,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533229</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2107,6 +2167,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533232</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2228,6 +2293,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533237</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2349,6 +2419,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533245</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2470,6 +2545,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533250</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2591,6 +2671,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533253</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2712,6 +2797,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69535244</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2821,6 +2911,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63217554</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2942,6 +3037,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537145</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3063,6 +3163,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537158</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3184,6 +3289,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533223</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3305,6 +3415,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533227</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3426,6 +3541,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533230</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3547,6 +3667,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533233</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3668,6 +3793,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533239</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3789,6 +3919,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533241</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3910,6 +4045,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533242</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4031,6 +4171,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533251</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4152,6 +4297,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533254</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4273,6 +4423,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533255</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4394,6 +4549,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533256</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4515,6 +4675,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69533257</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4640,6 +4805,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14216082</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4791,6 +4961,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57714558</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4910,6 +5085,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63217558</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5008,8 +5188,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108629192</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>